--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487143_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487143_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8702</v>
+        <v>1.0928</v>
       </c>
       <c r="E2" t="n">
-        <v>3.491</v>
+        <v>-0.5517</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6208</v>
+        <v>1.6445</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7673</v>
+        <v>0.915</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7833</v>
+        <v>-1.2813</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.016</v>
+        <v>2.1963</v>
       </c>
       <c r="J2" t="n">
-        <v>5.204</v>
+        <v>1.1285</v>
       </c>
       <c r="K2" t="n">
-        <v>2.665</v>
+        <v>-0.9472</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5391</v>
+        <v>2.0757</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.4368</v>
+        <v>-0.2135</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8817</v>
+        <v>-0.3341</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.5551</v>
+        <v>0.1207</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.0532</v>
+        <v>-0.193</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.7902</v>
+        <v>-1.9301</v>
       </c>
       <c r="R2" t="n">
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>4.379</v>
+        <v>0.3708</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5634</v>
+        <v>0.2499</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8157</v>
+        <v>0.1209</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7771</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3328</v>
+        <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1511</v>
+        <v>0.5938</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4839</v>
+        <v>0.3162</v>
       </c>
       <c r="G3" t="n">
-        <v>0.915</v>
+        <v>-1.7226</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2813</v>
+        <v>1.3641</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1963</v>
+        <v>-3.0867</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1285</v>
+        <v>-0.122</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9472</v>
+        <v>1.0504</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0757</v>
+        <v>-1.1724</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2135</v>
+        <v>-1.6006</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3341</v>
+        <v>0.3137</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1207</v>
+        <v>-1.9143</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6108</v>
+        <v>1.3468</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6504</v>
+        <v>0.781</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0397</v>
+        <v>0.5658</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,37 +721,37 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3175</v>
+        <v>-0.0562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8942</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4233</v>
+        <v>-0.722</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7226</v>
+        <v>-0.4675</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3641</v>
+        <v>-0.384</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.0867</v>
+        <v>-0.0835</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.122</v>
+        <v>1.841</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0504</v>
+        <v>0.0102</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1724</v>
+        <v>1.8308</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6006</v>
+        <v>-2.3085</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3137</v>
+        <v>-0.3942</v>
       </c>
       <c r="O4" t="n">
         <v>-1.9143</v>
@@ -766,28 +766,28 @@
         <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7543</v>
+        <v>0.1481</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0814</v>
+        <v>-0.2102</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.3582</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8999</v>
+        <v>-0.1228</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5638</v>
+        <v>-0.3418</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2653</v>
+        <v>1.9482</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-2.29</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4675</v>
+        <v>0.7673</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.384</v>
+        <v>1.7833</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0835</v>
+        <v>-1.016</v>
       </c>
       <c r="J5" t="n">
-        <v>1.841</v>
+        <v>5.204</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0102</v>
+        <v>2.665</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8308</v>
+        <v>2.5391</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3085</v>
+        <v>-4.4368</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3942</v>
+        <v>-0.8817</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9143</v>
+        <v>-3.5551</v>
       </c>
       <c r="P5" t="n">
-        <v>0.386</v>
+        <v>-4.0532</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-5.7902</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3596</v>
+        <v>2.1671</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6107</v>
+        <v>1.0206</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2512</v>
+        <v>1.1464</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1228</v>
+        <v>0.7771</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1228</v>
+        <v>-0.7368</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8302</v>
+        <v>-0.6904</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3915</v>
+        <v>-0.091</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4388</v>
+        <v>-0.5994</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6444</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9769</v>
+        <v>1.1167</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4442</v>
+        <v>0.2835</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5138</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9372</v>
+        <v>-2.4097</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9347</v>
+        <v>-0.434</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0025</v>
+        <v>-1.9757</v>
       </c>
       <c r="G7" t="n">
         <v>-2.8361</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0919</v>
+        <v>0.6194</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1494</v>
+        <v>0.3513</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2413</v>
+        <v>0.268</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9263</v>
+        <v>-2.9318</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.212</v>
+        <v>-2.3514</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7143</v>
+        <v>-0.5804</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4776</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6536999999999999</v>
+        <v>0.3407</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8037</v>
+        <v>0.0569</v>
       </c>
       <c r="U8" t="n">
-        <v>0.15</v>
+        <v>0.2839</v>
       </c>
       <c r="V8" t="n">
         <v>0.3281</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9736</v>
+        <v>-3.7069</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1551</v>
+        <v>-1.9954</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8185</v>
+        <v>-1.7115</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8177</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2261</v>
+        <v>0.0407</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5816</v>
+        <v>-0.422</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3556</v>
+        <v>0.4627</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1228</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5578</v>
+        <v>-6.538</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2527</v>
+        <v>-3.3935</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3051</v>
+        <v>-3.1445</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4204</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2498</v>
+        <v>-0.23</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1507</v>
+        <v>-0.2915</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0992</v>
+        <v>0.0614</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9225</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.375999999999999</v>
+        <v>-7.675</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3946</v>
+        <v>-5.9346</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9814</v>
+        <v>-1.7404</v>
       </c>
       <c r="G11" t="n">
         <v>-7.9193</v>
@@ -1312,13 +1312,13 @@
         <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9829</v>
+        <v>-0.2819</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7733</v>
+        <v>-0.3133</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2095</v>
+        <v>0.0314</v>
       </c>
       <c r="V11" t="n">
         <v>1.1052</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.6444</v>
+        <v>-22.347</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.8412</v>
+        <v>-11.5438</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.8033</v>
+        <v>-10.8032</v>
       </c>
       <c r="G12" t="n">
         <v>-21.6233</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6004999999999994</v>
+        <v>0.6005000000000003</v>
       </c>
       <c r="I12" t="n">
         <v>-22.2238</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0943</v>
+        <v>1.094300000000001</v>
       </c>
       <c r="K12" t="n">
         <v>4.8428</v>
@@ -1390,13 +1390,13 @@
         <v>12.5456</v>
       </c>
       <c r="S12" t="n">
-        <v>5.340800000000001</v>
+        <v>5.638399999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7586</v>
+        <v>2.0559</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5825</v>
+        <v>3.5822</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5716000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1358</v>
+        <v>10.3667</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7936</v>
+        <v>6.2929</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3422</v>
+        <v>4.0738</v>
       </c>
       <c r="G13" t="n">
         <v>6.2516</v>
@@ -1468,13 +1468,13 @@
         <v>3.4741</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2043</v>
+        <v>0.4352</v>
       </c>
       <c r="T13" t="n">
-        <v>0.16</v>
+        <v>-0.3407</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0443</v>
+        <v>0.776</v>
       </c>
       <c r="V13" t="n">
         <v>1.1708</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9758</v>
+        <v>7.4124</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6853</v>
+        <v>6.186</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2905</v>
+        <v>1.2264</v>
       </c>
       <c r="G14" t="n">
         <v>7.082</v>
@@ -1546,13 +1546,13 @@
         <v>3.2811</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0491</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9967</v>
+        <v>-0.496</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0523</v>
+        <v>-0.1164</v>
       </c>
       <c r="V14" t="n">
         <v>0.5568</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5162</v>
+        <v>5.0629</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6792</v>
+        <v>1.28</v>
       </c>
       <c r="F15" t="n">
-        <v>3.837</v>
+        <v>3.7828</v>
       </c>
       <c r="G15" t="n">
         <v>1.7908</v>
@@ -1624,13 +1624,13 @@
         <v>3.2811</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7615</v>
+        <v>-0.2148</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3537</v>
+        <v>-0.7528</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="V15" t="n">
         <v>1.1708</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6856</v>
+        <v>2.3805</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5531</v>
+        <v>0.8608</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1325</v>
+        <v>1.5197</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3649</v>
+        <v>3.7511</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4271</v>
+        <v>-0.4688</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9378</v>
+        <v>4.2199</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7167</v>
+        <v>3.4235</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8213</v>
+        <v>0.119</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8954</v>
+        <v>3.3045</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6482</v>
+        <v>0.3276</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3942</v>
+        <v>-0.5878</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0424</v>
+        <v>0.9154</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>1.092</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4807</v>
+        <v>-0.6325</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3887</v>
+        <v>-0.1018</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9993</v>
+        <v>-0.0572</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2851</v>
+        <v>-0.0572</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8061</v>
+        <v>1.5305</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6606</v>
+        <v>1.051</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1455</v>
+        <v>0.4795</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7511</v>
+        <v>3.3649</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4688</v>
+        <v>1.4271</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2199</v>
+        <v>1.9378</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4235</v>
+        <v>2.7167</v>
       </c>
       <c r="K17" t="n">
-        <v>0.119</v>
+        <v>1.8213</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3045</v>
+        <v>0.8954</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3276</v>
+        <v>0.6482</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5878</v>
+        <v>-0.3942</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9154</v>
+        <v>1.0424</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3088</v>
+        <v>-0.0631</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8328</v>
+        <v>-0.0214</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4759</v>
+        <v>-0.0417</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0572</v>
+        <v>-0.9993</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0572</v>
+        <v>-1.2851</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2349</v>
+        <v>-0.108</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0207</v>
+        <v>0.1208</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2556</v>
+        <v>-0.2289</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2528</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0178</v>
+        <v>0.1448</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3832</v>
+        <v>-0.1968</v>
       </c>
       <c r="E19" t="n">
         <v>-2.239</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8557</v>
+        <v>2.0421</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5155999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>2.8951</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5275</v>
+        <v>-0.3411</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5671</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0396</v>
+        <v>0.226</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2702</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3171</v>
+        <v>-0.2483</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1931</v>
+        <v>-1.7925</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8759</v>
+        <v>1.5442</v>
       </c>
       <c r="G20" t="n">
         <v>0.6725</v>
@@ -2014,13 +2014,13 @@
         <v>2.7021</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7966</v>
+        <v>-0.7277</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9373</v>
+        <v>-0.5367</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8593</v>
+        <v>-0.191</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5397</v>
+        <v>-0.885</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1573</v>
+        <v>-0.957</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3824</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5211</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2116</v>
+        <v>-0.5569</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5354</v>
+        <v>-0.3351</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6762</v>
+        <v>-0.2218</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>22.6446</v>
+        <v>25.3149</v>
       </c>
       <c r="E22" t="n">
-        <v>10.8031</v>
+        <v>10.803</v>
       </c>
       <c r="F22" t="n">
-        <v>11.8413</v>
+        <v>14.5116</v>
       </c>
       <c r="G22" t="n">
         <v>21.6234</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6006000000000006</v>
+        <v>-0.6006000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>22.2238</v>
@@ -2146,7 +2146,7 @@
         <v>22.7177</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2424</v>
+        <v>4.242400000000001</v>
       </c>
       <c r="L22" t="n">
         <v>18.4753</v>
@@ -2161,7 +2161,7 @@
         <v>3.7484</v>
       </c>
       <c r="P22" t="n">
-        <v>5.7903</v>
+        <v>5.790299999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.5454</v>
@@ -2170,22 +2170,22 @@
         <v>18.3356</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.341</v>
+        <v>-2.6704</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.5823</v>
+        <v>-3.5822</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7585</v>
+        <v>0.9119000000000002</v>
       </c>
       <c r="V22" t="n">
         <v>0.5717000000000003</v>
       </c>
       <c r="W22" t="n">
-        <v>4.213500000000001</v>
+        <v>4.2135</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.641699999999999</v>
+        <v>-3.6417</v>
       </c>
     </row>
   </sheetData>
